--- a/output/pdf_financials_xlsx/PJX.xlsx
+++ b/output/pdf_financials_xlsx/PJX.xlsx
@@ -1120,7 +1120,7 @@
         <v>-1.559037</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1.188186</v>
+        <v>-1.188186</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>-6.043586</v>
@@ -1340,7 +1340,7 @@
         <v>-1.481121</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1.188186</v>
+        <v>-1.188186</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>-6.043586</v>
@@ -1469,7 +1469,7 @@
         <v>-1.481121</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>1.188186</v>
+        <v>-1.188186</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>-6.043586</v>
@@ -1649,7 +1649,7 @@
         <v>-1.559037</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1.188186</v>
+        <v>-1.188186</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-6.043586</v>
@@ -1735,7 +1735,7 @@
         <v>-1.559037</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>1.213129</v>
+        <v>-1.163243</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-6.02234</v>
@@ -1845,7 +1845,7 @@
         <v>-4.997700503580094</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>-0</v>
@@ -17113,7 +17113,7 @@
         </is>
       </c>
       <c r="N150" s="5" t="n">
-        <v>1.188186</v>
+        <v>-1.188186</v>
       </c>
       <c r="O150" s="5" t="n">
         <v>-6.043586</v>

--- a/output/pdf_financials_xlsx/PJX.xlsx
+++ b/output/pdf_financials_xlsx/PJX.xlsx
@@ -951,10 +951,10 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002244</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.07828</v>
       </c>
     </row>
     <row r="13">
@@ -1652,10 +1652,10 @@
         <v>-1.188186</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-6.043586</v>
+        <v>-6.041342</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-2.046964</v>
+        <v>-1.968684</v>
       </c>
     </row>
     <row r="28">
@@ -1738,10 +1738,10 @@
         <v>-1.163243</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-6.02234</v>
+        <v>-6.020096</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.032338</v>
+        <v>-1.954058</v>
       </c>
     </row>
     <row r="30">
@@ -1935,31 +1935,31 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.444396</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.599703</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.8471070000000001</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2.987455</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.572886</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>2.22467</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.259561</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>2.637608</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.963443</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>2.703606</v>
@@ -1968,7 +1968,7 @@
         <v>2.584824</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.677004</v>
       </c>
     </row>
     <row r="35">
@@ -2021,31 +2021,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.444396</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.599703</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.8471070000000001</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>2.987455</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.572886</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>2.22467</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.259561</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>2.637608</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.963443</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>2.703606</v>
@@ -2054,7 +2054,7 @@
         <v>2.584824</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.677004</v>
       </c>
     </row>
     <row r="37">
@@ -2537,31 +2537,31 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.452832</v>
+        <v>0.008436000000000001</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.608203</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.855607</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.991622</v>
+        <v>0.004167</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.625827</v>
+        <v>0.052941</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.267679</v>
+        <v>0.043009</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.338713</v>
+        <v>0.079152</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>2.806976</v>
+        <v>0.169368</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.285377</v>
+        <v>0.321934</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0.031323</v>
@@ -2570,7 +2570,7 @@
         <v>0.030962</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.695935</v>
+        <v>0.018931</v>
       </c>
     </row>
     <row r="49">
@@ -5853,10 +5853,10 @@
         <v>0</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.009075</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.004721</v>
       </c>
       <c r="L124" s="3" t="n">
         <v>0</v>
@@ -5896,10 +5896,10 @@
         <v>0</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.009075</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.004721</v>
       </c>
       <c r="L125" s="3" t="n">
         <v>0</v>
@@ -6494,7 +6494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -11872,7 +11872,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -16778,7 +16782,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">

--- a/output/pdf_financials_xlsx/PJX.xlsx
+++ b/output/pdf_financials_xlsx/PJX.xlsx
@@ -5276,16 +5276,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.0035</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.07946400000000001</v>
       </c>
       <c r="J111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.016588</v>
       </c>
       <c r="L111" s="3" t="n">
         <v>0</v>
@@ -6313,16 +6313,16 @@
         <v>0</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.0035</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.07946400000000001</v>
       </c>
       <c r="J134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.016588</v>
       </c>
       <c r="L134" s="3" t="n">
         <v>0</v>
@@ -6356,16 +6356,16 @@
         <v>-2.126014</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-2.292888</v>
+        <v>-2.296388</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-0.77152</v>
+        <v>-0.850984</v>
       </c>
       <c r="J135" s="3" t="n">
         <v>-1.66509</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-0.843274</v>
+        <v>-0.859862</v>
       </c>
       <c r="L135" s="3" t="n">
         <v>-3.766432</v>
@@ -11286,7 +11286,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -12936,7 +12940,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -13902,7 +13910,11 @@
           <t>Deferred tax recoveries</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -15110,7 +15122,11 @@
           <t>Deferred tax recoveries 14</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -15794,7 +15810,11 @@
           <t>Deferred tax recoveries 13</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E132" s="5" t="n">
         <v>-0.040985</v>
       </c>
@@ -18402,7 +18422,11 @@
           <t>Interest revenue</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
